--- a/DeviMaya_S388017/Timesheet Devi Maya.xlsx
+++ b/DeviMaya_S388017/Timesheet Devi Maya.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/devi/Documents/GitHub/PRT585-SOFTWARE-ENGINEERING-PRACTICE/DeviMaya_S388017/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D952FD-538C-5148-B010-923029E661B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB912E8-C7A8-8A4D-9692-551270ACA346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Individual timesheet" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="57">
   <si>
     <t>EACH INDIVIDUAL MUST HAVE TO ENTER 6 HOURS TIME LOGGING IN THIS PAGE PER EACH WEEK</t>
   </si>
@@ -206,6 +206,18 @@
   </si>
   <si>
     <t>DA: self-study system design, dropbox case study (finish conceptual entity list, capacity estimation practice)</t>
+  </si>
+  <si>
+    <t>Week-7</t>
+  </si>
+  <si>
+    <t>DA: self-study system design, dropbox case study (finish ERD)</t>
+  </si>
+  <si>
+    <t>BA: self-study system design, dropbox case study (finish API design)</t>
+  </si>
+  <si>
+    <t>Project work: review &amp; prepare week 8 group assessment</t>
   </si>
 </sst>
 </file>
@@ -1194,37 +1206,139 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="4">
+        <v>1</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="4">
+        <v>2</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E37"/>
     </row>
-    <row r="38" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E38"/>
     </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E39"/>
     </row>
-    <row r="40" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E40"/>
     </row>
-    <row r="41" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E41"/>
     </row>
-    <row r="42" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E42" s="23"/>
     </row>
-    <row r="43" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E43" s="23"/>
     </row>
-    <row r="44" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E44" s="23"/>
     </row>
-    <row r="45" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E45" s="23"/>
     </row>
-    <row r="46" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E46" s="23"/>
     </row>
-    <row r="47" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E47" s="23"/>
     </row>
     <row r="49" spans="4:5" x14ac:dyDescent="0.2">
@@ -1956,6 +2070,74 @@
       <c r="B22"/>
       <c r="C22"/>
     </row>
+    <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>54</v>
+      </c>
+    </row>
     <row r="37" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E37"/>
     </row>
@@ -2397,6 +2579,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008A37478F0D103C418E1983367D0E3B29" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0e52e73692c282c4b11ce339126e795d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1a01afa4-83d8-4578-8116-1fe20cdd06b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d364ad524074f3044f8606d9c9b001a2" ns2:_="">
     <xsd:import namespace="1a01afa4-83d8-4578-8116-1fe20cdd06b6"/>
@@ -2534,12 +2722,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D5DBCEA-0785-438C-AB6D-531696C8FF28}">
   <ds:schemaRefs>
@@ -2549,6 +2731,15 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57E2D867-194E-458C-A857-FF5EE3277888}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC89AADA-5F80-4891-A851-84363269EAD3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2564,13 +2755,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57E2D867-194E-458C-A857-FF5EE3277888}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/DeviMaya_S388017/Timesheet Devi Maya.xlsx
+++ b/DeviMaya_S388017/Timesheet Devi Maya.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/devi/Documents/GitHub/PRT585-SOFTWARE-ENGINEERING-PRACTICE/DeviMaya_S388017/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/devi/Documents/GitHub/group01_software_project/DeviMaya_S388017/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB912E8-C7A8-8A4D-9692-551270ACA346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3250A47F-5168-0645-BF23-48691DF6013E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="60">
   <si>
     <t>EACH INDIVIDUAL MUST HAVE TO ENTER 6 HOURS TIME LOGGING IN THIS PAGE PER EACH WEEK</t>
   </si>
@@ -218,6 +218,15 @@
   </si>
   <si>
     <t>Project work: review &amp; prepare week 8 group assessment</t>
+  </si>
+  <si>
+    <t>Week-8</t>
+  </si>
+  <si>
+    <t>Project work: finish week 8 group assessment</t>
+  </si>
+  <si>
+    <t>Individual study: Consistent Hashing (https://www.hellointerview.com/learn/system-design/core-concepts/consistent-hashing)</t>
   </si>
 </sst>
 </file>
@@ -373,7 +382,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -435,6 +444,9 @@
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1311,23 +1323,107 @@
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E37"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E38"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E39"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E40"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E41"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E42" s="23"/>
+    <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="4">
+        <v>1</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="4">
+        <v>2</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A41" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E43" s="23"/>
+      <c r="A43" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B43" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E43" s="26" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E44" s="23"/>
@@ -2579,12 +2675,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008A37478F0D103C418E1983367D0E3B29" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0e52e73692c282c4b11ce339126e795d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1a01afa4-83d8-4578-8116-1fe20cdd06b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d364ad524074f3044f8606d9c9b001a2" ns2:_="">
     <xsd:import namespace="1a01afa4-83d8-4578-8116-1fe20cdd06b6"/>
@@ -2722,6 +2812,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D5DBCEA-0785-438C-AB6D-531696C8FF28}">
   <ds:schemaRefs>
@@ -2731,15 +2827,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57E2D867-194E-458C-A857-FF5EE3277888}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC89AADA-5F80-4891-A851-84363269EAD3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2755,4 +2842,13 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57E2D867-194E-458C-A857-FF5EE3277888}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/DeviMaya_S388017/Timesheet Devi Maya.xlsx
+++ b/DeviMaya_S388017/Timesheet Devi Maya.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/devi/Documents/GitHub/group01_software_project/DeviMaya_S388017/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3250A47F-5168-0645-BF23-48691DF6013E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C33FD49-E3F4-E34C-B4B5-3ED432F56317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="67">
   <si>
     <t>EACH INDIVIDUAL MUST HAVE TO ENTER 6 HOURS TIME LOGGING IN THIS PAGE PER EACH WEEK</t>
   </si>
@@ -227,6 +227,27 @@
   </si>
   <si>
     <t>Individual study: Consistent Hashing (https://www.hellointerview.com/learn/system-design/core-concepts/consistent-hashing)</t>
+  </si>
+  <si>
+    <t>Week-9</t>
+  </si>
+  <si>
+    <t>BA: self-study system design, dropbox case study (finish trade-off notes)</t>
+  </si>
+  <si>
+    <t>DA: self-study system design, dropbox case study (finish database picking analysis)</t>
+  </si>
+  <si>
+    <t>BA: self-study interview question practice</t>
+  </si>
+  <si>
+    <t>dA: self-study interview question practice</t>
+  </si>
+  <si>
+    <t>Individual study: CAP Theorem (https://www.hellointerview.com/learn/system-design/core-concepts/cap-theorem)</t>
+  </si>
+  <si>
+    <t>Individual study: Concurrency (https://www.hellointerview.com/learn/low-level-design/concurrency/intro)</t>
   </si>
 </sst>
 </file>
@@ -1428,21 +1449,107 @@
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E44" s="23"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E45" s="23"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E46" s="23"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E47" s="23"/>
-    </row>
-    <row r="49" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="E49" s="9"/>
-    </row>
-    <row r="50" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D50" s="10"/>
-      <c r="E50" s="9"/>
+    <row r="45" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="4">
+        <v>1</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B46" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="4">
+        <v>2</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A48" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B48" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B49" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B50" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E50" s="26" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E67" s="4"/>
@@ -2234,37 +2341,173 @@
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E37"/>
     </row>
-    <row r="38" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E38"/>
     </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E39"/>
     </row>
-    <row r="40" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E40"/>
     </row>
-    <row r="41" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E41"/>
     </row>
-    <row r="42" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E42" s="23"/>
     </row>
-    <row r="43" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E43" s="23"/>
     </row>
-    <row r="44" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E44" s="23"/>
     </row>
-    <row r="45" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E45" s="23"/>
     </row>
-    <row r="46" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E46" s="23"/>
     </row>
-    <row r="47" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E47" s="23"/>
     </row>
     <row r="49" spans="4:5" x14ac:dyDescent="0.2">
@@ -2675,6 +2918,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008A37478F0D103C418E1983367D0E3B29" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0e52e73692c282c4b11ce339126e795d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1a01afa4-83d8-4578-8116-1fe20cdd06b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d364ad524074f3044f8606d9c9b001a2" ns2:_="">
     <xsd:import namespace="1a01afa4-83d8-4578-8116-1fe20cdd06b6"/>
@@ -2812,12 +3061,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D5DBCEA-0785-438C-AB6D-531696C8FF28}">
   <ds:schemaRefs>
@@ -2827,6 +3070,15 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57E2D867-194E-458C-A857-FF5EE3277888}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC89AADA-5F80-4891-A851-84363269EAD3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2842,13 +3094,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57E2D867-194E-458C-A857-FF5EE3277888}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>